--- a/data/trans_orig/P16A06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A06-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>16187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +783,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>20118</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>13030</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>29570</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>20118</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>12423</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>29888</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>677604</t>
+          <t>676807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>689035</t>
+          <t>689147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>668862</t>
+          <t>668325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>681865</t>
+          <t>682099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +896,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1361227</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1351775</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1368315</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>99,06%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1357</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1361227</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1351457</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1368922</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25330</t>
+          <t>25603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>22170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45368</t>
+          <t>45388</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>35322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65039</t>
+          <t>63809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>936470</t>
+          <t>936197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>953189</t>
+          <t>952523</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>923025</t>
+          <t>923005</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>946285</t>
+          <t>946223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1865154</t>
+          <t>1866384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1894472</t>
+          <t>1894871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22252</t>
+          <t>21811</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27437</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51092</t>
+          <t>49714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38042</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64170</t>
+          <t>65636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656257</t>
+          <t>656698</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>671659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>632749</t>
+          <t>634127</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656404</t>
+          <t>656474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1298180</t>
+          <t>1296714</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324308</t>
+          <t>1324209</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>19342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40024</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45622</t>
+          <t>46312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76607</t>
+          <t>75236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70204</t>
+          <t>70647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107485</t>
+          <t>108393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>902198</t>
+          <t>902642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922835</t>
+          <t>922880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>962005</t>
+          <t>963376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>992990</t>
+          <t>992300</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1873349</t>
+          <t>1872441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1910630</t>
+          <t>1910187</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50520</t>
+          <t>50187</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80965</t>
+          <t>82874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>116772</t>
+          <t>118361</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>164191</t>
+          <t>165057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180172</t>
+          <t>176275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>235616</t>
+          <t>233535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3194560</t>
+          <t>3192651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3225005</t>
+          <t>3225338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3215006</t>
+          <t>3214140</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3262425</t>
+          <t>3260836</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6419106</t>
+          <t>6421187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6474550</t>
+          <t>6478447</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21864</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24032</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46012</t>
+          <t>45719</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34372</t>
+          <t>34052</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60698</t>
+          <t>59846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>679715</t>
+          <t>680937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>694383</t>
+          <t>694304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>646325</t>
+          <t>646618</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>668305</t>
+          <t>668938</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1333217</t>
+          <t>1334069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1359543</t>
+          <t>1359863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62585</t>
+          <t>61640</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98323</t>
+          <t>98945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72248</t>
+          <t>72404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109749</t>
+          <t>110925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996438</t>
+          <t>996371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1010525</t>
+          <t>1010635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>929452</t>
+          <t>928830</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>965190</t>
+          <t>966135</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1933912</t>
+          <t>1932736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1971413</t>
+          <t>1971257</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31111</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58062</t>
+          <t>57066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45228</t>
+          <t>45617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78881</t>
+          <t>80567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>725427</t>
+          <t>726376</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>746327</t>
+          <t>746361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>718221</t>
+          <t>719217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>746779</t>
+          <t>747427</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1453940</t>
+          <t>1452254</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1487593</t>
+          <t>1487204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17597</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40645</t>
+          <t>42012</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54112</t>
+          <t>53378</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84899</t>
+          <t>85978</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77090</t>
+          <t>78919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118081</t>
+          <t>118363</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>903294</t>
+          <t>901927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>926342</t>
+          <t>925787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>963864</t>
+          <t>962785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>994651</t>
+          <t>995385</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1874622</t>
+          <t>1874340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1915613</t>
+          <t>1913784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52781</t>
+          <t>54220</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>88623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192835</t>
+          <t>196652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>254178</t>
+          <t>251511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>258055</t>
+          <t>263880</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>326046</t>
+          <t>331559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3327918</t>
+          <t>3329318</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3365160</t>
+          <t>3363721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3290981</t>
+          <t>3293648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3352324</t>
+          <t>3348507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6637054</t>
+          <t>6631541</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6705045</t>
+          <t>6699220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>26147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74880</t>
+          <t>73900</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59186</t>
+          <t>59624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93949</t>
+          <t>92613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649447</t>
+          <t>648653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665327</t>
+          <t>665085</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>597959</t>
+          <t>598939</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>627759</t>
+          <t>628653</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1253690</t>
+          <t>1255026</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1288453</t>
+          <t>1288015</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>16251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38035</t>
+          <t>38238</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46065</t>
+          <t>44588</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75978</t>
+          <t>75856</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>67953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102358</t>
+          <t>103963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>984396</t>
+          <t>984193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1006318</t>
+          <t>1006180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>966935</t>
+          <t>967057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>996848</t>
+          <t>998325</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1962986</t>
+          <t>1961381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2000144</t>
+          <t>1997391</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40241</t>
+          <t>39270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70288</t>
+          <t>70013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57810</t>
+          <t>57400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92226</t>
+          <t>93064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>730318</t>
+          <t>730378</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>748309</t>
+          <t>747896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>714723</t>
+          <t>714998</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>744770</t>
+          <t>745741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1452337</t>
+          <t>1451499</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1486753</t>
+          <t>1487163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>41475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74605</t>
+          <t>75967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117376</t>
+          <t>116153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102181</t>
+          <t>103190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148729</t>
+          <t>147709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896210</t>
+          <t>896092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>918332</t>
+          <t>917628</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>926403</t>
+          <t>927626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>969174</t>
+          <t>967812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1832617</t>
+          <t>1833637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1879165</t>
+          <t>1878156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73728</t>
+          <t>71362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112248</t>
+          <t>109099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234670</t>
+          <t>234505</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>297806</t>
+          <t>301382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>318409</t>
+          <t>320372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>399037</t>
+          <t>396633</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3282102</t>
+          <t>3285251</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3320622</t>
+          <t>3322988</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3246736</t>
+          <t>3243160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3309872</t>
+          <t>3310037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6539855</t>
+          <t>6542259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6620483</t>
+          <t>6618520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32790</t>
+          <t>31935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55199</t>
+          <t>55741</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71720</t>
+          <t>70608</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94790</t>
+          <t>95583</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107657</t>
+          <t>107901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143107</t>
+          <t>142960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>579752</t>
+          <t>579210</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>602161</t>
+          <t>603016</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>580632</t>
+          <t>579839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>603702</t>
+          <t>604814</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1167266</t>
+          <t>1167413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1202716</t>
+          <t>1202472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50695</t>
+          <t>50696</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76978</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105075</t>
+          <t>105667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84329</t>
+          <t>85738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152530</t>
+          <t>151782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1142169</t>
+          <t>1142168</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1173934</t>
+          <t>1175525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>852871</t>
+          <t>852279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>880968</t>
+          <t>880647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1998280</t>
+          <t>1999028</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2066481</t>
+          <t>2065072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>24175</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44693</t>
+          <t>45391</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32241</t>
+          <t>32490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91872</t>
+          <t>92471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61377</t>
+          <t>65299</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121841</t>
+          <t>123083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658991</t>
+          <t>658293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679409</t>
+          <t>679509</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>840768</t>
+          <t>840169</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>900399</t>
+          <t>900150</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1514482</t>
+          <t>1513240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1574946</t>
+          <t>1571024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44133</t>
+          <t>44846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72940</t>
+          <t>73047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95608</t>
+          <t>94006</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144260</t>
+          <t>141363</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152832</t>
+          <t>152764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203572</t>
+          <t>204919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853891</t>
+          <t>853784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882698</t>
+          <t>881985</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>947114</t>
+          <t>950011</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>995766</t>
+          <t>997368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1814633</t>
+          <t>1813286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1865373</t>
+          <t>1865441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131136</t>
+          <t>129731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>196992</t>
+          <t>193911</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>304452</t>
+          <t>291033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>401918</t>
+          <t>399005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>455011</t>
+          <t>459592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>578475</t>
+          <t>580537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3261338</t>
+          <t>3264419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3327194</t>
+          <t>3328599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3255463</t>
+          <t>3258376</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3352929</t>
+          <t>3366348</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6537237</t>
+          <t>6535175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6660701</t>
+          <t>6656120</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A06-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20026</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29570</t>
+          <t>31452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>676807</t>
+          <t>676874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>689147</t>
+          <t>689094</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>668325</t>
+          <t>668392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>682099</t>
+          <t>682375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1351775</t>
+          <t>1349893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1368315</t>
+          <t>1368174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25603</t>
+          <t>26173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45388</t>
+          <t>46038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35322</t>
+          <t>35063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>62548</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>936197</t>
+          <t>935627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>952523</t>
+          <t>953087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>923005</t>
+          <t>922355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1866384</t>
+          <t>1867645</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1894871</t>
+          <t>1895130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21811</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27367</t>
+          <t>26946</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49714</t>
+          <t>50090</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65636</t>
+          <t>66566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656698</t>
+          <t>656644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>671659</t>
+          <t>671963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>634127</t>
+          <t>633751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656474</t>
+          <t>656895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1296714</t>
+          <t>1295784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324209</t>
+          <t>1324185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19342</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39580</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46312</t>
+          <t>44940</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75236</t>
+          <t>76061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70647</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108393</t>
+          <t>107685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>902642</t>
+          <t>903527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922880</t>
+          <t>922828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>963376</t>
+          <t>962551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>992300</t>
+          <t>993672</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1872441</t>
+          <t>1873149</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1910187</t>
+          <t>1909380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82874</t>
+          <t>83533</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118361</t>
+          <t>118772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>165057</t>
+          <t>165490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>176275</t>
+          <t>180315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>233535</t>
+          <t>234048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3192651</t>
+          <t>3191992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3225338</t>
+          <t>3224183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3214140</t>
+          <t>3213707</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3260836</t>
+          <t>3260425</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6421187</t>
+          <t>6420674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6478447</t>
+          <t>6474407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20642</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23399</t>
+          <t>24358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45719</t>
+          <t>47095</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>34747</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59846</t>
+          <t>60922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>680937</t>
+          <t>679582</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>694304</t>
+          <t>694584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>646618</t>
+          <t>645242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>668938</t>
+          <t>667979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1334069</t>
+          <t>1332993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1359863</t>
+          <t>1359168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61640</t>
+          <t>63597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98945</t>
+          <t>98561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72404</t>
+          <t>72596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110925</t>
+          <t>110898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996371</t>
+          <t>996695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1010635</t>
+          <t>1010527</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>928830</t>
+          <t>929214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>966135</t>
+          <t>964178</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1932736</t>
+          <t>1932763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1971257</t>
+          <t>1971065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>32127</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28856</t>
+          <t>29918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57066</t>
+          <t>55470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45617</t>
+          <t>44760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80567</t>
+          <t>78583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>726376</t>
+          <t>724411</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>746361</t>
+          <t>746389</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>719217</t>
+          <t>720813</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>747427</t>
+          <t>746365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1452254</t>
+          <t>1454238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1487204</t>
+          <t>1488061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>18650</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42012</t>
+          <t>42072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53378</t>
+          <t>53295</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85978</t>
+          <t>85172</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78919</t>
+          <t>78247</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118363</t>
+          <t>118963</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>901927</t>
+          <t>901867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>925787</t>
+          <t>925289</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>962785</t>
+          <t>963591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>995385</t>
+          <t>995468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1874340</t>
+          <t>1873740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1913784</t>
+          <t>1914456</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54220</t>
+          <t>51830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88623</t>
+          <t>89358</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196652</t>
+          <t>196237</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>251511</t>
+          <t>252201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>263880</t>
+          <t>260782</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>331559</t>
+          <t>331267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3329318</t>
+          <t>3328583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3363721</t>
+          <t>3366111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3293648</t>
+          <t>3292958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3348507</t>
+          <t>3348922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6631541</t>
+          <t>6631833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6699220</t>
+          <t>6702318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26147</t>
+          <t>26851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44186</t>
+          <t>43403</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73900</t>
+          <t>72881</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59624</t>
+          <t>59220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92613</t>
+          <t>94051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>648653</t>
+          <t>647949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665085</t>
+          <t>665243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>598939</t>
+          <t>599958</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>628653</t>
+          <t>629436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1255026</t>
+          <t>1253588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1288015</t>
+          <t>1288419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16251</t>
+          <t>16431</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38238</t>
+          <t>37389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44588</t>
+          <t>45962</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75856</t>
+          <t>75669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67953</t>
+          <t>67840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103963</t>
+          <t>105677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>984193</t>
+          <t>985042</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1006180</t>
+          <t>1006000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>967057</t>
+          <t>967244</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>998325</t>
+          <t>996951</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1961381</t>
+          <t>1959667</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1997391</t>
+          <t>1997504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>29351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>40510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70013</t>
+          <t>71312</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57400</t>
+          <t>56586</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93064</t>
+          <t>93075</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>730378</t>
+          <t>730201</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>747896</t>
+          <t>748791</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>714998</t>
+          <t>713699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>745741</t>
+          <t>744501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1451499</t>
+          <t>1451488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1487163</t>
+          <t>1487977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41475</t>
+          <t>41775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75967</t>
+          <t>74314</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116153</t>
+          <t>115557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103190</t>
+          <t>101062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147709</t>
+          <t>148479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896092</t>
+          <t>895792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>917628</t>
+          <t>917151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>927626</t>
+          <t>928222</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>967812</t>
+          <t>969465</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1833637</t>
+          <t>1832867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1878156</t>
+          <t>1880284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>113046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234505</t>
+          <t>237364</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>301382</t>
+          <t>302058</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>320372</t>
+          <t>320580</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>396633</t>
+          <t>395757</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3285251</t>
+          <t>3281304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3322988</t>
+          <t>3321764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3243160</t>
+          <t>3242484</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3310037</t>
+          <t>3307178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6542259</t>
+          <t>6543135</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6618520</t>
+          <t>6618312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42129</t>
+          <t>44846</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31935</t>
+          <t>33208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55741</t>
+          <t>58228</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>82541</t>
+          <t>88298</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70608</t>
+          <t>74197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95583</t>
+          <t>101676</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>124670</t>
+          <t>133144</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107901</t>
+          <t>116464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142960</t>
+          <t>153278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>592822</t>
+          <t>645369</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>579210</t>
+          <t>631987</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603016</t>
+          <t>657007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>592881</t>
+          <t>644484</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>579839</t>
+          <t>631106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>604814</t>
+          <t>658585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1185703</t>
+          <t>1289853</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1167413</t>
+          <t>1269719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1202472</t>
+          <t>1306533</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35301</t>
+          <t>40091</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>29853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50696</t>
+          <t>54014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91105</t>
+          <t>99460</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77299</t>
+          <t>84588</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105667</t>
+          <t>116121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>126405</t>
+          <t>139551</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85738</t>
+          <t>120152</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151782</t>
+          <t>161420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1157563</t>
+          <t>1008826</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1142168</t>
+          <t>994903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1175525</t>
+          <t>1019064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>866841</t>
+          <t>970664</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>852279</t>
+          <t>954003</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>880647</t>
+          <t>985536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2024405</t>
+          <t>1979490</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1999028</t>
+          <t>1957621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2065072</t>
+          <t>1998889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957946</t>
+          <t>1070124</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957946</t>
+          <t>1070124</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957946</t>
+          <t>1070124</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150810</t>
+          <t>2119041</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150810</t>
+          <t>2119041</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150810</t>
+          <t>2119041</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33294</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24175</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45391</t>
+          <t>53814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66224</t>
+          <t>72697</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32490</t>
+          <t>60622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92471</t>
+          <t>89250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>99518</t>
+          <t>112205</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65299</t>
+          <t>94660</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123083</t>
+          <t>132390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>670390</t>
+          <t>762579</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658293</t>
+          <t>748272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679509</t>
+          <t>773997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>866416</t>
+          <t>738257</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>840169</t>
+          <t>721704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>900150</t>
+          <t>750332</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1536805</t>
+          <t>1500835</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1513240</t>
+          <t>1480650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1571024</t>
+          <t>1518380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932640</t>
+          <t>810954</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932640</t>
+          <t>810954</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932640</t>
+          <t>810954</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636323</t>
+          <t>1613040</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636323</t>
+          <t>1613040</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636323</t>
+          <t>1613040</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57059</t>
+          <t>57328</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44846</t>
+          <t>45022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73047</t>
+          <t>74815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>120049</t>
+          <t>126774</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94006</t>
+          <t>110279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141363</t>
+          <t>143885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>177108</t>
+          <t>184102</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152764</t>
+          <t>164179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204919</t>
+          <t>206096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>869772</t>
+          <t>932734</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853784</t>
+          <t>915247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>881985</t>
+          <t>945040</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>971325</t>
+          <t>990257</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>950011</t>
+          <t>973146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>997368</t>
+          <t>1006752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1841097</t>
+          <t>1922991</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1813286</t>
+          <t>1900997</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1865441</t>
+          <t>1942914</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>167783</t>
+          <t>181771</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>129731</t>
+          <t>158617</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193911</t>
+          <t>210388</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>359919</t>
+          <t>387229</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>291033</t>
+          <t>357335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>399005</t>
+          <t>418483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>527702</t>
+          <t>569001</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>459592</t>
+          <t>529545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>580537</t>
+          <t>610851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3290547</t>
+          <t>3349509</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3264419</t>
+          <t>3320892</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3328599</t>
+          <t>3372663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3297462</t>
+          <t>3343662</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3258376</t>
+          <t>3312408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3366348</t>
+          <t>3373556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6588010</t>
+          <t>6693169</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6535175</t>
+          <t>6651319</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6656120</t>
+          <t>6732625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657381</t>
+          <t>3730891</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657381</t>
+          <t>3730891</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657381</t>
+          <t>3730891</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7115712</t>
+          <t>7262170</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7115712</t>
+          <t>7262170</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7115712</t>
+          <t>7262170</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
